--- a/docs/sample-output/06-retail-pad-qsr/estimate.xlsx
+++ b/docs/sample-output/06-retail-pad-qsr/estimate.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="368">
   <si>
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Outparcel QSR with drive-thru · Total $4,048,466</t>
+    <t>Total Project Cost — Summary   ·   Outparcel QSR with drive-thru · Total $4,046,356</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   Outparcel QSR with drive-thru · Total $4,048,466</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   Outparcel QSR with drive-thru · Total $4,046,356</t>
   </si>
   <si>
     <t>Component</t>
@@ -147,7 +147,7 @@
     <t>within ($397–$1,359)</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Outparcel QSR with drive-thru · Total $4,048,466</t>
+    <t>Cost by Phase   ·   Outparcel QSR with drive-thru · Total $4,046,356</t>
   </si>
   <si>
     <t>Phase</t>
@@ -189,7 +189,7 @@
     <t>4.2%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Outparcel QSR with drive-thru · Total $4,048,466</t>
+    <t>Line-Item Detail   ·   Outparcel QSR with drive-thru · Total $4,046,356</t>
   </si>
   <si>
     <t>Group</t>
@@ -465,7 +465,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Outparcel QSR with drive-thru · Total $4,048,466</t>
+    <t>Draw Schedules   ·   Outparcel QSR with drive-thru · Total $4,046,356</t>
   </si>
   <si>
     <t>PHASE 1 — MONTHLY DRAWS</t>
@@ -504,7 +504,7 @@
     <t>2027-11</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Outparcel QSR with drive-thru · Total $4,048,466</t>
+    <t>Sources &amp; Assumptions   ·   Outparcel QSR with drive-thru · Total $4,046,356</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -540,7 +540,7 @@
     <t>LTC 60%, rate 7.00%, fee 1.00%</t>
   </si>
   <si>
-    <t>SOURCES (49)</t>
+    <t>SOURCES (50)</t>
   </si>
   <si>
     <t>Ref</t>
@@ -1105,6 +1105,21 @@
   </si>
   <si>
     <t>https://www.tdlr.texas.gov/TABS/Projects/TABS2025010278</t>
+  </si>
+  <si>
+    <t>residential/single-family.json#e10</t>
+  </si>
+  <si>
+    <t>Cost of Constructing a Home-2024 (Special Study for Housing Economics)</t>
+  </si>
+  <si>
+    <t>National Association of Home Builders (Eric Lynch)</t>
+  </si>
+  <si>
+    <t>26747 USD/unit (2024)</t>
+  </si>
+  <si>
+    <t>https://nahb.org/-/media/AB4EFC742624475A97A0A62189986FF8.ashx</t>
   </si>
 </sst>
 </file>
@@ -1702,7 +1717,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>26258.17</v>
+        <v>24426.83</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1710,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>106538.6</v>
+        <v>106459.49</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1718,7 +1733,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>69862.25</v>
+        <v>69809.57</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1726,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>23898.8</v>
+        <v>23752.3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1734,7 +1749,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>507468.04</v>
+        <v>505358.41</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1750,7 +1765,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1789,7 +1804,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>4482230.081428572</v>
+        <v>4479894.419642857</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1917,19 +1932,19 @@
         <v>2332397.84</v>
       </c>
       <c r="E5" s="13">
-        <v>507468.04</v>
+        <v>505358.41</v>
       </c>
       <c r="F5" s="13">
         <v>1208600</v>
       </c>
       <c r="G5" s="13">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
       <c r="H5" s="13">
-        <v>1445.8806714285713</v>
+        <v>1445.127232142857</v>
       </c>
       <c r="I5" s="14">
-        <v>1445.8806714285713</v>
+        <v>1445.127232142857</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>42</v>
@@ -1945,13 +1960,13 @@
         <v>2332397.84</v>
       </c>
       <c r="E6" s="16">
-        <v>507468.04</v>
+        <v>505358.41</v>
       </c>
       <c r="F6" s="16">
         <v>1208600</v>
       </c>
       <c r="G6" s="16">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -2067,19 +2082,19 @@
         <v>2332397.84</v>
       </c>
       <c r="G5" s="13">
-        <v>507468.04</v>
+        <v>505358.41</v>
       </c>
       <c r="H5" s="13">
         <v>1208600</v>
       </c>
       <c r="I5" s="13">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
       <c r="J5" s="13">
-        <v>2429079.53</v>
+        <v>2427813.75</v>
       </c>
       <c r="K5" s="13">
-        <v>45571.45</v>
+        <v>45531.43</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2094,13 +2109,13 @@
         <v>2332397.84</v>
       </c>
       <c r="G6" s="16">
-        <v>507468.04</v>
+        <v>505358.41</v>
       </c>
       <c r="H6" s="16">
         <v>1208600</v>
       </c>
       <c r="I6" s="16">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -3237,10 +3252,10 @@
         <v>133</v>
       </c>
       <c r="H40" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I40" s="13">
-        <v>3386.73</v>
+        <v>2385.05</v>
       </c>
       <c r="J40" s="12" t="s">
         <v>69</v>
@@ -3269,10 +3284,10 @@
         <v>133</v>
       </c>
       <c r="H41" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I41" s="13">
-        <v>3214.71</v>
+        <v>2385.05</v>
       </c>
       <c r="J41" s="12" t="s">
         <v>69</v>
@@ -3302,7 +3317,7 @@
       </c>
       <c r="H42" s="18"/>
       <c r="I42" s="13">
-        <v>23898.8</v>
+        <v>23752.3</v>
       </c>
       <c r="J42" s="12" t="s">
         <v>69</v>
@@ -3448,7 +3463,7 @@
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="13">
-        <v>106538.6</v>
+        <v>106459.49</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>69</v>
@@ -3476,7 +3491,7 @@
       </c>
       <c r="H48" s="18"/>
       <c r="I48" s="13">
-        <v>45571.45</v>
+        <v>45531.43</v>
       </c>
       <c r="J48" s="12" t="s">
         <v>69</v>
@@ -3504,7 +3519,7 @@
       </c>
       <c r="H49" s="18"/>
       <c r="I49" s="13">
-        <v>24290.8</v>
+        <v>24278.14</v>
       </c>
       <c r="J49" s="12" t="s">
         <v>69</v>
@@ -3524,7 +3539,7 @@
       <c r="G50" s="15"/>
       <c r="H50" s="15"/>
       <c r="I50" s="16">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
       <c r="J50" s="15"/>
     </row>
@@ -3623,13 +3638,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>194162.63</v>
+        <v>192331.29</v>
       </c>
       <c r="D6" s="13">
         <v>1208600</v>
       </c>
       <c r="E6" s="13">
-        <v>1427053.43</v>
+        <v>1425209.43</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -3649,13 +3664,13 @@
         <v>88771.59</v>
       </c>
       <c r="C7" s="13">
-        <v>30430.44</v>
+        <v>30402.24</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>119202.03</v>
+        <v>119173.83</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -3675,22 +3690,22 @@
         <v>252800.19</v>
       </c>
       <c r="C8" s="13">
-        <v>30430.42</v>
+        <v>30402.22</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>73130.89</v>
+        <v>74159.24</v>
       </c>
       <c r="F8" s="13">
-        <v>210099.72</v>
+        <v>209043.17</v>
       </c>
       <c r="G8" s="13">
         <v>0</v>
       </c>
       <c r="H8" s="13">
-        <v>210099.72</v>
+        <v>209043.17</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3701,7 +3716,7 @@
         <v>378342.13</v>
       </c>
       <c r="C9" s="13">
-        <v>30430.41</v>
+        <v>30402.21</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
@@ -3710,13 +3725,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="13">
-        <v>408772.54</v>
+        <v>408744.34</v>
       </c>
       <c r="G9" s="13">
-        <v>1225.58</v>
+        <v>1219.42</v>
       </c>
       <c r="H9" s="13">
-        <v>620097.84</v>
+        <v>619006.93</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3727,7 +3742,7 @@
         <v>446285.01</v>
       </c>
       <c r="C10" s="13">
-        <v>30430.41</v>
+        <v>30402.21</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
@@ -3736,13 +3751,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="13">
-        <v>476715.42</v>
+        <v>476687.22</v>
       </c>
       <c r="G10" s="13">
-        <v>3617.24</v>
+        <v>3610.87</v>
       </c>
       <c r="H10" s="13">
-        <v>1100430.5</v>
+        <v>1099305.02</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3753,7 +3768,7 @@
         <v>446284.96</v>
       </c>
       <c r="C11" s="13">
-        <v>30430.38</v>
+        <v>30402.19</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
@@ -3762,13 +3777,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="13">
-        <v>476715.34</v>
+        <v>476687.15</v>
       </c>
       <c r="G11" s="13">
-        <v>6419.18</v>
+        <v>6412.61</v>
       </c>
       <c r="H11" s="13">
-        <v>1583565.02</v>
+        <v>1582404.78</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3779,7 +3794,7 @@
         <v>378342.19</v>
       </c>
       <c r="C12" s="13">
-        <v>30430.37</v>
+        <v>30402.17</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
@@ -3788,13 +3803,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>408772.56</v>
+        <v>408744.36</v>
       </c>
       <c r="G12" s="13">
-        <v>9237.46</v>
+        <v>9230.69</v>
       </c>
       <c r="H12" s="13">
-        <v>2001575.04</v>
+        <v>2000379.83</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3805,7 +3820,7 @@
         <v>252800.19</v>
       </c>
       <c r="C13" s="13">
-        <v>30430.37</v>
+        <v>30402.16</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
@@ -3814,13 +3829,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>283230.56</v>
+        <v>283202.35</v>
       </c>
       <c r="G13" s="13">
-        <v>11675.85</v>
+        <v>11668.88</v>
       </c>
       <c r="H13" s="13">
-        <v>2296481.45</v>
+        <v>2295251.06</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3831,7 +3846,7 @@
         <v>88771.58</v>
       </c>
       <c r="C14" s="13">
-        <v>30430.36</v>
+        <v>30402.15</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
@@ -3840,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>119201.94</v>
+        <v>119173.73</v>
       </c>
       <c r="G14" s="13">
-        <v>13396.14</v>
+        <v>13388.96</v>
       </c>
       <c r="H14" s="13">
-        <v>2429079.53</v>
+        <v>2427813.75</v>
       </c>
     </row>
   </sheetData>
@@ -3868,7 +3883,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4953,6 +4968,26 @@
       </c>
       <c r="F60" s="12" t="s">
         <v>362</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
